--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2872" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2872" uniqueCount="525">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:49:57+00:00</t>
+    <t>2026-08-28T07:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -285,7 +285,7 @@
 dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
-    <t>LDH</t>
+    <t>MM3</t>
   </si>
   <si>
     <t>Event</t>
@@ -1239,6 +1239,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
+  </si>
+  <si>
+    <t>MM3 (Komponente)</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -7791,30 +7794,30 @@
         <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>88</v>
+        <v>392</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7837,19 +7840,19 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7898,7 +7901,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7922,7 +7925,7 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7933,10 +7936,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7962,13 +7965,13 @@
         <v>235</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7997,10 +8000,10 @@
         <v>158</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8018,7 +8021,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8039,24 +8042,24 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8082,16 +8085,16 @@
         <v>235</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8119,10 +8122,10 @@
         <v>158</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8140,7 +8143,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8164,7 +8167,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8175,10 +8178,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8201,16 +8204,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8260,7 +8263,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8281,24 +8284,24 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8321,16 +8324,16 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8380,7 +8383,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8401,24 +8404,24 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8441,19 +8444,19 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8502,7 +8505,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8514,7 +8517,7 @@
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8526,7 +8529,7 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8537,10 +8540,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8655,10 +8658,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8775,14 +8778,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8804,10 +8807,10 @@
         <v>113</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>116</v>
@@ -8862,7 +8865,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8897,10 +8900,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8923,13 +8926,13 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8980,7 +8983,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8989,7 +8992,7 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
@@ -9004,7 +9007,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9015,10 +9018,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9041,13 +9044,13 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9098,7 +9101,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9107,7 +9110,7 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
@@ -9122,7 +9125,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9133,10 +9136,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9162,16 +9165,16 @@
         <v>235</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9199,10 +9202,10 @@
         <v>172</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9220,7 +9223,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9241,10 +9244,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9255,10 +9258,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9284,16 +9287,16 @@
         <v>235</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9321,10 +9324,10 @@
         <v>158</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9342,7 +9345,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9363,10 +9366,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9377,10 +9380,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9403,17 +9406,17 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9462,7 +9465,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9497,10 +9500,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9526,10 +9529,10 @@
         <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9580,7 +9583,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9604,7 +9607,7 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9615,10 +9618,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9641,16 +9644,16 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9700,7 +9703,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9724,7 +9727,7 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -9735,10 +9738,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9761,16 +9764,16 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9820,7 +9823,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9844,7 +9847,7 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -9855,10 +9858,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9881,19 +9884,19 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -9942,7 +9945,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9966,7 +9969,7 @@
         <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -9977,10 +9980,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10095,10 +10098,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10215,14 +10218,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10244,10 +10247,10 @@
         <v>113</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>116</v>
@@ -10302,7 +10305,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10337,10 +10340,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10366,13 +10369,13 @@
         <v>235</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O70" t="s" s="2">
         <v>265</v>
@@ -10424,7 +10427,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>93</v>
@@ -10445,7 +10448,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>270</v>
@@ -10459,10 +10462,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10485,16 +10488,16 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O71" t="s" s="2">
         <v>331</v>
@@ -10546,7 +10549,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10567,7 +10570,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>334</v>
@@ -10581,10 +10584,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10610,13 +10613,13 @@
         <v>235</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>379</v>
@@ -10668,7 +10671,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10703,10 +10706,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10732,10 +10735,10 @@
         <v>235</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>388</v>
@@ -10790,7 +10793,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10811,24 +10814,24 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10854,16 +10857,16 @@
         <v>83</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -10912,7 +10915,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10936,7 +10939,7 @@
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:57:18+00:00</t>
+    <t>2026-08-28T14:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-ldh.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
